--- a/lang/uk/headTags.xlsx
+++ b/lang/uk/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1198</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2250">
   <si>
     <t>en</t>
   </si>
@@ -5455,6 +5455,18 @@
     <t>Шулкер.</t>
   </si>
   <si>
+    <t>Sift (Inspired)</t>
+  </si>
+  <si>
+    <t>Sift (Натхненний)</t>
+  </si>
+  <si>
+    <t>Sift (Vanilla)</t>
+  </si>
+  <si>
+    <t>Sift (Ваніль)</t>
+  </si>
+  <si>
     <t>Silent Hill</t>
   </si>
   <si>
@@ -6316,6 +6328,12 @@
     <t>ULTRAKILL</t>
   </si>
   <si>
+    <t>Umamusume</t>
+  </si>
+  <si>
+    <t>Умамасуме</t>
+  </si>
+  <si>
     <t>Umineko - When They Cry</t>
   </si>
   <si>
@@ -6596,6 +6614,12 @@
   </si>
   <si>
     <t>Зима</t>
+  </si>
+  <si>
+    <t>Winter Drop</t>
+  </si>
+  <si>
+    <t>Зимова колекція</t>
   </si>
   <si>
     <t>Witcher</t>
@@ -7089,7 +7113,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1194"/>
+  <dimension ref="A1:B1198"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14805,20 +14829,20 @@
         <v>1814</v>
       </c>
       <c r="B964" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B965" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="B966" t="s">
         <v>1818</v>
@@ -14925,20 +14949,20 @@
         <v>1843</v>
       </c>
       <c r="B979" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="B980" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="B981" t="s">
         <v>1847</v>
@@ -15005,20 +15029,20 @@
         <v>1862</v>
       </c>
       <c r="B989" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B990" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="B991" t="s">
         <v>1866</v>
@@ -15037,20 +15061,20 @@
         <v>1869</v>
       </c>
       <c r="B993" t="s">
-        <v>1868</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="B994" t="s">
-        <v>1870</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1871</v>
+        <v>1873</v>
       </c>
       <c r="B995" t="s">
         <v>1872</v>
@@ -15058,7 +15082,7 @@
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="B996" t="s">
         <v>1874</v>
@@ -15077,20 +15101,20 @@
         <v>1877</v>
       </c>
       <c r="B998" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="B999" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B1000" t="s">
         <v>1881</v>
@@ -15173,20 +15197,20 @@
         <v>1900</v>
       </c>
       <c r="B1010" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="B1011" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="B1012" t="s">
         <v>1904</v>
@@ -15237,20 +15261,20 @@
         <v>1915</v>
       </c>
       <c r="B1018" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="B1019" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="B1020" t="s">
         <v>1919</v>
@@ -15317,20 +15341,20 @@
         <v>1934</v>
       </c>
       <c r="B1028" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="B1029" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="B1030" t="s">
         <v>1938</v>
@@ -15341,20 +15365,20 @@
         <v>1939</v>
       </c>
       <c r="B1031" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="B1032" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="B1033" t="s">
         <v>1943</v>
@@ -15413,28 +15437,28 @@
         <v>1956</v>
       </c>
       <c r="B1040" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="B1041" t="s">
-        <v>1957</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="B1042" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="B1043" t="s">
         <v>1961</v>
@@ -15445,36 +15469,36 @@
         <v>1962</v>
       </c>
       <c r="B1044" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="B1045" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="B1046" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="B1047" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="B1048" t="s">
         <v>1969</v>
@@ -15501,20 +15525,20 @@
         <v>1974</v>
       </c>
       <c r="B1051" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B1052" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="B1053" t="s">
         <v>1978</v>
@@ -15557,20 +15581,20 @@
         <v>1987</v>
       </c>
       <c r="B1058" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="B1059" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="B1060" t="s">
         <v>1991</v>
@@ -15589,20 +15613,20 @@
         <v>1994</v>
       </c>
       <c r="B1062" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="B1063" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="B1064" t="s">
         <v>1998</v>
@@ -15613,20 +15637,20 @@
         <v>1999</v>
       </c>
       <c r="B1065" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="B1066" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B1067" t="s">
         <v>2003</v>
@@ -15733,20 +15757,20 @@
         <v>2028</v>
       </c>
       <c r="B1080" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="B1081" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="B1082" t="s">
         <v>2032</v>
@@ -15765,20 +15789,20 @@
         <v>2035</v>
       </c>
       <c r="B1084" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="B1085" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="B1086" t="s">
         <v>2039</v>
@@ -15805,36 +15829,36 @@
         <v>2044</v>
       </c>
       <c r="B1089" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="B1090" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="B1091" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="B1092" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="B1093" t="s">
         <v>2051</v>
@@ -16029,60 +16053,60 @@
         <v>2098</v>
       </c>
       <c r="B1117" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="B1118" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="B1119" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="B1120" t="s">
-        <v>2102</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="B1121" t="s">
-        <v>2103</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>2104</v>
+        <v>2107</v>
       </c>
       <c r="B1122" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="B1123" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="B1124" t="s">
         <v>2109</v>
@@ -16325,44 +16349,44 @@
         <v>2168</v>
       </c>
       <c r="B1154" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="B1155" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="B1156" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="B1157" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="B1158" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="B1159" t="s">
         <v>2177</v>
@@ -16397,28 +16421,28 @@
         <v>2184</v>
       </c>
       <c r="B1163" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="B1164" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="B1165" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="B1166" t="s">
         <v>2190</v>
@@ -16477,36 +16501,36 @@
         <v>2203</v>
       </c>
       <c r="B1173" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="B1174" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="B1175" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="B1176" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="B1177" t="s">
         <v>2211</v>
@@ -16517,36 +16541,36 @@
         <v>2212</v>
       </c>
       <c r="B1178" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="B1179" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="B1180" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="B1181" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="B1182" t="s">
         <v>2220</v>
@@ -16557,60 +16581,60 @@
         <v>2221</v>
       </c>
       <c r="B1183" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="B1184" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="B1185" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="B1186" t="s">
-        <v>2226</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="B1187" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="B1188" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="B1189" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="B1190" t="s">
         <v>2234</v>
@@ -16629,27 +16653,59 @@
         <v>2237</v>
       </c>
       <c r="B1192" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="B1193" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="B1194" t="s">
-        <v>2241</v>
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:2">
+      <c r="A1195" t="s">
+        <v>2243</v>
+      </c>
+      <c r="B1195" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:2">
+      <c r="A1196" t="s">
+        <v>2245</v>
+      </c>
+      <c r="B1196" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:2">
+      <c r="A1197" t="s">
+        <v>2246</v>
+      </c>
+      <c r="B1197" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:2">
+      <c r="A1198" t="s">
+        <v>2248</v>
+      </c>
+      <c r="B1198" t="s">
+        <v>2249</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1194"/>
+  <autoFilter ref="A1:B1198"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
